--- a/input/timetable/Лечебное дело_иностр_.xlsx
+++ b/input/timetable/Лечебное дело_иностр_.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="167">
   <si>
     <t>пара</t>
   </si>
@@ -255,9 +255,6 @@
     <t>Фармакология, п/г 1, А434//</t>
   </si>
   <si>
-    <t>Топографическая анатомия и оперативная хирургия, п/г 3, А24</t>
-  </si>
-  <si>
     <t>501-16</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
     <t>//Химия, п/г 3, А124</t>
   </si>
   <si>
-    <t>Иностранный язык (англ),п/г 3, К518</t>
-  </si>
-  <si>
     <t>Сестринское дело, п/г 1, А30//</t>
   </si>
   <si>
@@ -435,12 +429,6 @@
     <t>Лучевая диагностика, п/г 2, СОКБ//</t>
   </si>
   <si>
-    <t>Лучевая диагностика, п/г 3, СОКБ// Топографическая анатомия и оперативная хирургия, п/г2, А24</t>
-  </si>
-  <si>
-    <t>Топографическая анатомия и оперативная хирургия, п/г 2, А24</t>
-  </si>
-  <si>
     <t>Патологическая анатомия, п/г 1, А539</t>
   </si>
   <si>
@@ -468,18 +456,9 @@
     <t>Иностранный язык в профессиональной сфере (русский язык),(24 ч), п/г3, А539</t>
   </si>
   <si>
-    <t xml:space="preserve">Топографическая анатомия и оперативная хирургия, п/г 1, А439// </t>
-  </si>
-  <si>
-    <t>Топографическая анатомия и оперативная хирургия, п/г 1, А439</t>
-  </si>
-  <si>
     <t>Иностранный язык в профессиональной сфере (русский язык) п/г2, К526</t>
   </si>
   <si>
-    <t>//Топографическая анатомия и оперативная хирургия, п/г 3, А24</t>
-  </si>
-  <si>
     <t>Факультетская терапия (лекция 16 ч), ЭОиДОТ//Иммунология и аллергология (лекция 16 ч), ЭОиДОТ</t>
   </si>
   <si>
@@ -495,9 +474,6 @@
     <t>Эндокринология (лекция), ЭОиДОТ// Госпитальная терапия (лекция), ЭОиДОТ</t>
   </si>
   <si>
-    <t>Гинекология (лекция  8ч), СОКЦОМиД// Акушерство (лекция 12 ч), СОКЦОМиД</t>
-  </si>
-  <si>
     <t>Психиатрия, медицинская  психология (лекция), ЭОиДОТ//Госпитальная хирургия, детская хирургия (лекция), ЭОиДОТ</t>
   </si>
   <si>
@@ -556,6 +532,33 @@
   </si>
   <si>
     <t>Биохимия, п/г 1, А433</t>
+  </si>
+  <si>
+    <t>Иностранный язык (англ),п/г 3, К428</t>
+  </si>
+  <si>
+    <t>//Топографическая анатомия и оперативная хирургия, п/г 3, СОКБ, ауд 5</t>
+  </si>
+  <si>
+    <t>Топографическая анатомия и оперативная хирургия, п/г 3, СОКБ ауд 5</t>
+  </si>
+  <si>
+    <t>Топографическая анатомия и оперативная хирургия, п/г 1, СОКБ ауд 5</t>
+  </si>
+  <si>
+    <t>Топографическая анатомия и оперативная хирургия, п/г 1, СОКБ ауд 5//</t>
+  </si>
+  <si>
+    <t>Лучевая диагностика, п/г 3, СОКБ// Топографическая анатомия и оперативная хирургия, п/г2, СОКБ ауд 5</t>
+  </si>
+  <si>
+    <t>Топографическая анатомия и оперативная хирургия, п/г 2, СОКБ ауд 5</t>
+  </si>
+  <si>
+    <t>// Акушерство (лекция 12 ч), СОКЦОМиД</t>
+  </si>
+  <si>
+    <t>// Гинекология (лекция  8ч), СОКЦОМиД</t>
   </si>
 </sst>
 </file>
@@ -1614,73 +1617,16 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="46" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1689,115 +1635,72 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1807,19 +1710,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1831,9 +1722,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1843,34 +1731,287 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1888,179 +2029,185 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2098,149 +2245,86 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2263,87 +2347,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2353,6 +2356,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2361,15 +2373,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2727,7 +2730,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>10</v>
@@ -2743,7 +2746,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2752,7 +2755,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
       <c r="H4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -2760,7 +2763,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2800,7 +2803,7 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
       <c r="G7" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>6</v>
@@ -2808,16 +2811,16 @@
     </row>
     <row r="8" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="18"/>
-      <c r="C8" s="103" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
+      <c r="C8" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -2843,100 +2846,100 @@
       <c r="B10" s="53">
         <v>2</v>
       </c>
-      <c r="C10" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
+      <c r="C10" s="107" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="133"/>
     </row>
     <row r="11" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="54"/>
       <c r="B11" s="55">
         <v>3</v>
       </c>
-      <c r="C11" s="112" t="s">
+      <c r="C11" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="117"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="119"/>
     </row>
     <row r="12" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="54"/>
       <c r="B12" s="55">
         <v>4</v>
       </c>
-      <c r="C12" s="118" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="120"/>
+      <c r="C12" s="120" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="122"/>
     </row>
     <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="54"/>
       <c r="B13" s="55">
         <v>5</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="85" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="83"/>
-      <c r="H13" s="86"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="123" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="124"/>
+      <c r="H13" s="125"/>
     </row>
     <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56"/>
       <c r="B14" s="57">
         <v>6</v>
       </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="85" t="s">
+      <c r="C14" s="126"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="86"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="125"/>
     </row>
     <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56"/>
       <c r="B15" s="57">
         <v>7</v>
       </c>
-      <c r="C15" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="85" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="83"/>
-      <c r="H15" s="86"/>
+      <c r="C15" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="124"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="123" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="124"/>
+      <c r="H15" s="125"/>
     </row>
     <row r="16" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="58"/>
       <c r="B16" s="59">
         <v>8</v>
       </c>
-      <c r="C16" s="93" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="94"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="132"/>
+      <c r="C16" s="146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="147"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="98"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="52" t="s">
@@ -2945,84 +2948,84 @@
       <c r="B17" s="53">
         <v>1</v>
       </c>
-      <c r="C17" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="75"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="G17" s="75"/>
-      <c r="H17" s="78"/>
+      <c r="C17" s="134" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="135"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="137" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="135"/>
+      <c r="H17" s="138"/>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="54"/>
       <c r="B18" s="55">
         <v>2</v>
       </c>
-      <c r="C18" s="133" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="134"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="136" t="s">
-        <v>161</v>
-      </c>
-      <c r="G18" s="134"/>
-      <c r="H18" s="137"/>
+      <c r="C18" s="86" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="75"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="74" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="75"/>
+      <c r="H18" s="76"/>
     </row>
     <row r="19" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="54"/>
       <c r="B19" s="55">
         <v>3</v>
       </c>
-      <c r="C19" s="133" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="134"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="136" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="137"/>
+      <c r="C19" s="86" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="75"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" s="75"/>
+      <c r="H19" s="76"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="54"/>
       <c r="B20" s="55">
         <v>4</v>
       </c>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="73"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="85"/>
     </row>
     <row r="21" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="54"/>
       <c r="B21" s="55">
         <v>5</v>
       </c>
-      <c r="C21" s="99" t="s">
+      <c r="C21" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="90"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="71"/>
     </row>
     <row r="22" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="60"/>
       <c r="B22" s="59"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="97"/>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="98"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="150"/>
+      <c r="G22" s="150"/>
+      <c r="H22" s="151"/>
     </row>
     <row r="23" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="52" t="s">
@@ -3031,88 +3034,88 @@
       <c r="B23" s="53">
         <v>3</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="127"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="80"/>
     </row>
     <row r="24" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="54"/>
       <c r="B24" s="53">
         <v>4</v>
       </c>
-      <c r="C24" s="138" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="139"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="136" t="s">
+      <c r="C24" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="134"/>
-      <c r="H24" s="137"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="75"/>
+      <c r="H24" s="76"/>
     </row>
     <row r="25" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="54"/>
       <c r="B25" s="55">
         <v>5</v>
       </c>
-      <c r="C25" s="138" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="136" t="s">
+      <c r="C25" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="134"/>
-      <c r="H25" s="137"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="75"/>
+      <c r="H25" s="76"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="54"/>
       <c r="B26" s="55">
         <v>6</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="C26" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="107"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="73"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="85"/>
     </row>
     <row r="27" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56"/>
       <c r="B27" s="57">
         <v>7</v>
       </c>
-      <c r="C27" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="89"/>
-      <c r="H27" s="90"/>
+      <c r="C27" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="71"/>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="60"/>
       <c r="B28" s="59">
         <v>8</v>
       </c>
-      <c r="C28" s="87"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="91"/>
-      <c r="H28" s="92"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="144"/>
+      <c r="H28" s="145"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="52" t="s">
@@ -3121,72 +3124,72 @@
       <c r="B29" s="53">
         <v>1</v>
       </c>
-      <c r="C29" s="100" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="102"/>
+      <c r="C29" s="152" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="154"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="54"/>
       <c r="B30" s="55">
         <v>2</v>
       </c>
-      <c r="C30" s="99" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89" t="s">
+      <c r="C30" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="89"/>
-      <c r="H30" s="90"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="71"/>
     </row>
     <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="54"/>
       <c r="B31" s="55">
         <v>3</v>
       </c>
-      <c r="C31" s="154" t="s">
+      <c r="C31" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="110"/>
-      <c r="H31" s="111"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="82"/>
+      <c r="H31" s="113"/>
     </row>
     <row r="32" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="56"/>
       <c r="B32" s="57">
         <v>4</v>
       </c>
-      <c r="C32" s="71"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="73"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="85"/>
     </row>
     <row r="33" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="60"/>
       <c r="B33" s="59">
         <v>6</v>
       </c>
-      <c r="C33" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="149"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="149"/>
-      <c r="G33" s="149"/>
-      <c r="H33" s="150"/>
+      <c r="C33" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="68"/>
     </row>
     <row r="34" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="52" t="s">
@@ -3195,80 +3198,80 @@
       <c r="B34" s="53">
         <v>3</v>
       </c>
-      <c r="C34" s="125"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="151" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="152"/>
-      <c r="G34" s="153"/>
-      <c r="H34" s="127"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="73"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="80"/>
     </row>
     <row r="35" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="51"/>
       <c r="B35" s="53">
         <v>4</v>
       </c>
-      <c r="C35" s="133" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" s="134"/>
-      <c r="E35" s="134"/>
-      <c r="F35" s="134"/>
-      <c r="G35" s="134"/>
-      <c r="H35" s="137"/>
+      <c r="C35" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="76"/>
     </row>
     <row r="36" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="61"/>
       <c r="B36" s="55">
         <v>5</v>
       </c>
-      <c r="C36" s="133" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="134"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="134"/>
-      <c r="G36" s="134"/>
-      <c r="H36" s="137"/>
+      <c r="C36" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="76"/>
     </row>
     <row r="37" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="61"/>
       <c r="B37" s="55"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="73"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="85"/>
     </row>
     <row r="38" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="62"/>
       <c r="B38" s="57">
         <v>7</v>
       </c>
-      <c r="C38" s="99" t="s">
+      <c r="C38" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="90"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="71"/>
     </row>
     <row r="39" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="63"/>
       <c r="B39" s="59">
         <v>8</v>
       </c>
-      <c r="C39" s="145" t="s">
+      <c r="C39" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="146"/>
-      <c r="E39" s="146"/>
-      <c r="F39" s="146"/>
-      <c r="G39" s="146"/>
-      <c r="H39" s="147"/>
+      <c r="D39" s="88"/>
+      <c r="E39" s="88"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="88"/>
+      <c r="H39" s="89"/>
     </row>
     <row r="40" spans="1:8" ht="20.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A40" s="64" t="s">
@@ -3277,70 +3280,70 @@
       <c r="B40" s="53">
         <v>1</v>
       </c>
-      <c r="C40" s="142" t="s">
+      <c r="C40" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="144"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="105"/>
     </row>
     <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="65"/>
       <c r="B41" s="53">
         <v>3</v>
       </c>
-      <c r="C41" s="141" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" s="128"/>
-      <c r="E41" s="128"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="129"/>
+      <c r="C41" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="92"/>
     </row>
     <row r="42" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="65"/>
       <c r="B42" s="55">
         <v>4</v>
       </c>
-      <c r="C42" s="141" t="s">
+      <c r="C42" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" s="91"/>
+      <c r="E42" s="91"/>
+      <c r="F42" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="128"/>
-      <c r="E42" s="128"/>
-      <c r="F42" s="128" t="s">
-        <v>102</v>
-      </c>
-      <c r="G42" s="128"/>
-      <c r="H42" s="129"/>
+      <c r="G42" s="91"/>
+      <c r="H42" s="92"/>
     </row>
     <row r="43" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A43" s="65"/>
       <c r="B43" s="59">
         <v>5</v>
       </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="68"/>
+      <c r="C43" s="129"/>
+      <c r="D43" s="130"/>
+      <c r="E43" s="130"/>
+      <c r="F43" s="130"/>
+      <c r="G43" s="130"/>
+      <c r="H43" s="131"/>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A44" s="21"/>
       <c r="B44" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="122" t="s">
+      <c r="C44" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="D44" s="123"/>
-      <c r="E44" s="123"/>
-      <c r="F44" s="123"/>
-      <c r="G44" s="123"/>
-      <c r="H44" s="124"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="95"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B45" s="2" t="s">
@@ -3360,19 +3363,32 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="F42:H42"/>
@@ -3389,32 +3405,19 @@
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="F25:H25"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C31:E31"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3470,7 +3473,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>10</v>
@@ -3493,7 +3496,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -3501,7 +3504,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3543,13 +3546,13 @@
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
+        <v>78</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
@@ -3572,64 +3575,64 @@
       <c r="B10" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="201" t="s">
+      <c r="C10" s="179" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="202"/>
-      <c r="E10" s="202"/>
-      <c r="F10" s="203"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="177"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="29"/>
       <c r="B11" s="33">
         <v>4</v>
       </c>
-      <c r="C11" s="189"/>
-      <c r="D11" s="190"/>
-      <c r="E11" s="173" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11" s="176"/>
+      <c r="C11" s="180"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="156" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="157"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="29"/>
       <c r="B12" s="32">
         <v>5</v>
       </c>
-      <c r="C12" s="172" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="173"/>
-      <c r="E12" s="160" t="s">
-        <v>163</v>
-      </c>
-      <c r="F12" s="161"/>
+      <c r="C12" s="155" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="156"/>
+      <c r="E12" s="162" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="163"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="29"/>
       <c r="B13" s="33">
         <v>6</v>
       </c>
-      <c r="C13" s="172" t="s">
-        <v>162</v>
-      </c>
-      <c r="D13" s="173"/>
-      <c r="E13" s="160" t="s">
-        <v>158</v>
-      </c>
-      <c r="F13" s="161"/>
+      <c r="C13" s="155" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="156"/>
+      <c r="E13" s="162" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" s="163"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="30"/>
       <c r="B14" s="34">
         <v>7</v>
       </c>
-      <c r="C14" s="155" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="157"/>
+      <c r="C14" s="201" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="203"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31" t="s">
@@ -3638,73 +3641,73 @@
       <c r="B15" s="32">
         <v>1</v>
       </c>
-      <c r="C15" s="170" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="171"/>
-      <c r="E15" s="174"/>
-      <c r="F15" s="175"/>
+      <c r="C15" s="212" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="213"/>
+      <c r="E15" s="214"/>
+      <c r="F15" s="215"/>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="32">
         <v>2</v>
       </c>
-      <c r="C16" s="172" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="173"/>
-      <c r="E16" s="173" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" s="176"/>
+      <c r="C16" s="155" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="157"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="29"/>
       <c r="B17" s="32">
         <v>3</v>
       </c>
-      <c r="C17" s="179" t="s">
-        <v>156</v>
-      </c>
-      <c r="D17" s="160"/>
-      <c r="E17" s="160"/>
-      <c r="F17" s="161"/>
+      <c r="C17" s="178" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="162"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="163"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="29"/>
       <c r="B18" s="32">
         <v>4</v>
       </c>
-      <c r="C18" s="187"/>
-      <c r="D18" s="188"/>
-      <c r="E18" s="160" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="161"/>
+      <c r="C18" s="189"/>
+      <c r="D18" s="190"/>
+      <c r="E18" s="162" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="163"/>
     </row>
     <row r="19" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="29"/>
       <c r="B19" s="33">
         <v>5</v>
       </c>
-      <c r="C19" s="189"/>
-      <c r="D19" s="190"/>
-      <c r="E19" s="173" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="176"/>
+      <c r="C19" s="180"/>
+      <c r="D19" s="181"/>
+      <c r="E19" s="156" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="157"/>
     </row>
     <row r="20" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="30"/>
       <c r="B20" s="34">
         <v>6</v>
       </c>
-      <c r="C20" s="208"/>
-      <c r="D20" s="209"/>
-      <c r="E20" s="177" t="s">
+      <c r="C20" s="164"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="216" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="178"/>
+      <c r="F20" s="217"/>
     </row>
     <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="28" t="s">
@@ -3713,10 +3716,10 @@
       <c r="B21" s="35">
         <v>1</v>
       </c>
-      <c r="C21" s="162"/>
-      <c r="D21" s="163"/>
-      <c r="E21" s="163"/>
-      <c r="F21" s="164"/>
+      <c r="C21" s="206"/>
+      <c r="D21" s="207"/>
+      <c r="E21" s="207"/>
+      <c r="F21" s="208"/>
     </row>
     <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="29"/>
@@ -3736,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="191" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D23" s="192"/>
       <c r="E23" s="192"/>
@@ -3748,7 +3751,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="194" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D24" s="195"/>
       <c r="E24" s="195"/>
@@ -3759,36 +3762,36 @@
       <c r="B25" s="33">
         <v>5</v>
       </c>
-      <c r="C25" s="168" t="s">
+      <c r="C25" s="172" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="169"/>
-      <c r="E25" s="160" t="s">
-        <v>164</v>
-      </c>
-      <c r="F25" s="161"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="162" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="163"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="36"/>
       <c r="B26" s="37">
         <v>6</v>
       </c>
-      <c r="C26" s="168" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="169"/>
-      <c r="E26" s="160" t="s">
-        <v>164</v>
-      </c>
-      <c r="F26" s="161"/>
+      <c r="C26" s="172" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="173"/>
+      <c r="E26" s="162" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" s="163"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="30"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="166"/>
-      <c r="E27" s="166"/>
-      <c r="F27" s="167"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="210"/>
+      <c r="E27" s="210"/>
+      <c r="F27" s="211"/>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="28" t="s">
@@ -3797,50 +3800,50 @@
       <c r="B28" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="213" t="s">
+      <c r="C28" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="214"/>
-      <c r="E28" s="214"/>
-      <c r="F28" s="215"/>
+      <c r="D28" s="170"/>
+      <c r="E28" s="170"/>
+      <c r="F28" s="171"/>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="29"/>
       <c r="B29" s="33">
         <v>4</v>
       </c>
-      <c r="C29" s="187"/>
-      <c r="D29" s="188"/>
-      <c r="E29" s="160" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="161"/>
+      <c r="C29" s="189"/>
+      <c r="D29" s="190"/>
+      <c r="E29" s="162" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="163"/>
     </row>
     <row r="30" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="29"/>
       <c r="B30" s="33">
         <v>5</v>
       </c>
-      <c r="C30" s="183"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="185" t="s">
-        <v>159</v>
-      </c>
-      <c r="F30" s="186"/>
+      <c r="C30" s="185"/>
+      <c r="D30" s="186"/>
+      <c r="E30" s="187" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="188"/>
     </row>
     <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="36"/>
       <c r="B31" s="37">
         <v>6</v>
       </c>
-      <c r="C31" s="172" t="s">
-        <v>165</v>
-      </c>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173" t="s">
+      <c r="C31" s="155" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="176"/>
+      <c r="F31" s="157"/>
     </row>
     <row r="32" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="36"/>
@@ -3848,7 +3851,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="197" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D32" s="198"/>
       <c r="E32" s="199"/>
@@ -3861,62 +3864,62 @@
       <c r="B33" s="35">
         <v>2</v>
       </c>
-      <c r="C33" s="158" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="159"/>
-      <c r="E33" s="160" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="161"/>
+      <c r="C33" s="204" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="205"/>
+      <c r="E33" s="162" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="163"/>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
       <c r="B34" s="32">
         <v>3</v>
       </c>
-      <c r="C34" s="180" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="181"/>
-      <c r="E34" s="181"/>
-      <c r="F34" s="182"/>
+      <c r="C34" s="182" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" s="183"/>
+      <c r="E34" s="183"/>
+      <c r="F34" s="184"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="39"/>
       <c r="B35" s="37">
         <v>4</v>
       </c>
-      <c r="C35" s="210" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" s="211"/>
-      <c r="E35" s="211"/>
-      <c r="F35" s="212"/>
+      <c r="C35" s="166" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" s="167"/>
+      <c r="E35" s="167"/>
+      <c r="F35" s="168"/>
     </row>
     <row r="36" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="39"/>
       <c r="B36" s="37">
         <v>5</v>
       </c>
-      <c r="C36" s="210" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" s="211"/>
-      <c r="E36" s="211"/>
-      <c r="F36" s="212"/>
+      <c r="C36" s="166" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="167"/>
+      <c r="E36" s="167"/>
+      <c r="F36" s="168"/>
     </row>
     <row r="37" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="40"/>
       <c r="B37" s="34">
         <v>6</v>
       </c>
-      <c r="C37" s="210" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="211"/>
-      <c r="E37" s="211"/>
-      <c r="F37" s="212"/>
+      <c r="C37" s="166" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="167"/>
+      <c r="E37" s="167"/>
+      <c r="F37" s="168"/>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="49" t="s">
@@ -3925,74 +3928,74 @@
       <c r="B38" s="35">
         <v>1</v>
       </c>
-      <c r="C38" s="216" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="217"/>
-      <c r="E38" s="202" t="s">
+      <c r="C38" s="174" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="175"/>
+      <c r="E38" s="176" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="203"/>
+      <c r="F38" s="177"/>
     </row>
     <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="41"/>
       <c r="B39" s="32">
         <v>2</v>
       </c>
-      <c r="C39" s="179" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="160"/>
-      <c r="E39" s="160" t="s">
-        <v>120</v>
-      </c>
-      <c r="F39" s="161"/>
+      <c r="C39" s="178" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="162"/>
+      <c r="E39" s="162" t="s">
+        <v>118</v>
+      </c>
+      <c r="F39" s="163"/>
     </row>
     <row r="40" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="41"/>
       <c r="B40" s="33">
         <v>3</v>
       </c>
-      <c r="C40" s="179" t="s">
+      <c r="C40" s="178" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="160"/>
-      <c r="E40" s="173" t="s">
-        <v>121</v>
-      </c>
-      <c r="F40" s="176"/>
+      <c r="D40" s="162"/>
+      <c r="E40" s="156" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="157"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="42"/>
       <c r="B41" s="37">
         <v>4</v>
       </c>
-      <c r="C41" s="172"/>
-      <c r="D41" s="173"/>
-      <c r="E41" s="173"/>
-      <c r="F41" s="176"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="157"/>
     </row>
     <row r="42" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="43"/>
       <c r="B42" s="34">
         <v>5</v>
       </c>
-      <c r="C42" s="204" t="s">
+      <c r="C42" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="205"/>
-      <c r="E42" s="205"/>
-      <c r="F42" s="206"/>
+      <c r="D42" s="159"/>
+      <c r="E42" s="159"/>
+      <c r="F42" s="160"/>
     </row>
     <row r="43" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="207" t="s">
+      <c r="A43" s="161" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="207"/>
-      <c r="C43" s="207"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="207"/>
-      <c r="F43" s="207"/>
+      <c r="B43" s="161"/>
+      <c r="C43" s="161"/>
+      <c r="D43" s="161"/>
+      <c r="E43" s="161"/>
+      <c r="F43" s="161"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B44" s="2" t="s">
@@ -4012,6 +4015,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="A43:F43"/>
@@ -4028,45 +4070,6 @@
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C17:F17"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -4122,7 +4125,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>10</v>
@@ -4138,14 +4141,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -4153,7 +4156,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -4195,13 +4198,13 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="103" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
@@ -4224,64 +4227,64 @@
       <c r="B10" s="32">
         <v>2</v>
       </c>
-      <c r="C10" s="265" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="255"/>
-      <c r="E10" s="266" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" s="267"/>
+      <c r="C10" s="248" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="238"/>
+      <c r="E10" s="218" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="219"/>
     </row>
     <row r="11" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="29"/>
       <c r="B11" s="32">
         <v>3</v>
       </c>
-      <c r="C11" s="210" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="211"/>
-      <c r="E11" s="271" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="272"/>
+      <c r="C11" s="166" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="167"/>
+      <c r="E11" s="223" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="224"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="29"/>
       <c r="B12" s="32">
         <v>4</v>
       </c>
-      <c r="C12" s="273" t="s">
+      <c r="C12" s="225" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="271"/>
-      <c r="E12" s="271"/>
-      <c r="F12" s="272"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="223"/>
+      <c r="F12" s="224"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="29"/>
       <c r="B13" s="32">
         <v>6</v>
       </c>
-      <c r="C13" s="275" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="276"/>
-      <c r="E13" s="276"/>
-      <c r="F13" s="277"/>
+      <c r="C13" s="227" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="229"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="29"/>
       <c r="B14" s="33">
         <v>7</v>
       </c>
-      <c r="C14" s="274" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
-      <c r="F14" s="178"/>
+      <c r="C14" s="226" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
+      <c r="F14" s="217"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="28" t="s">
@@ -4290,36 +4293,36 @@
       <c r="B15" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="268" t="s">
+      <c r="C15" s="220" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="269"/>
-      <c r="E15" s="269"/>
-      <c r="F15" s="270"/>
+      <c r="D15" s="221"/>
+      <c r="E15" s="221"/>
+      <c r="F15" s="222"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="29"/>
       <c r="B16" s="32">
         <v>4</v>
       </c>
-      <c r="C16" s="180" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="181"/>
-      <c r="E16" s="181"/>
-      <c r="F16" s="182"/>
+      <c r="C16" s="182" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="184"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="29"/>
       <c r="B17" s="33">
         <v>5</v>
       </c>
-      <c r="C17" s="210" t="s">
+      <c r="C17" s="166" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="211"/>
-      <c r="E17" s="231" t="s">
-        <v>131</v>
+      <c r="D17" s="167"/>
+      <c r="E17" s="233" t="s">
+        <v>127</v>
       </c>
       <c r="F17" s="196"/>
     </row>
@@ -4328,12 +4331,12 @@
       <c r="B18" s="33">
         <v>6</v>
       </c>
-      <c r="C18" s="180" t="s">
+      <c r="C18" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="230"/>
-      <c r="E18" s="231" t="s">
-        <v>131</v>
+      <c r="D18" s="252"/>
+      <c r="E18" s="233" t="s">
+        <v>127</v>
       </c>
       <c r="F18" s="196"/>
     </row>
@@ -4342,10 +4345,10 @@
       <c r="B19" s="33">
         <v>7</v>
       </c>
-      <c r="C19" s="218"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="220"/>
-      <c r="F19" s="221"/>
+      <c r="C19" s="266"/>
+      <c r="D19" s="267"/>
+      <c r="E19" s="268"/>
+      <c r="F19" s="269"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="28" t="s">
@@ -4354,12 +4357,12 @@
       <c r="B20" s="35">
         <v>1</v>
       </c>
-      <c r="C20" s="263"/>
-      <c r="D20" s="264"/>
-      <c r="E20" s="255" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="256"/>
+      <c r="C20" s="246"/>
+      <c r="D20" s="247"/>
+      <c r="E20" s="238" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="239"/>
     </row>
     <row r="21" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="48"/>
@@ -4367,11 +4370,11 @@
         <v>2</v>
       </c>
       <c r="C21" s="191" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="222"/>
-      <c r="E21" s="223" t="s">
-        <v>72</v>
+        <v>128</v>
+      </c>
+      <c r="D21" s="270"/>
+      <c r="E21" s="271" t="s">
+        <v>71</v>
       </c>
       <c r="F21" s="193"/>
     </row>
@@ -4380,48 +4383,48 @@
       <c r="B22" s="32">
         <v>3</v>
       </c>
-      <c r="C22" s="172" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="173"/>
-      <c r="E22" s="257"/>
-      <c r="F22" s="258"/>
+      <c r="C22" s="155" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="156"/>
+      <c r="E22" s="240"/>
+      <c r="F22" s="241"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="29"/>
       <c r="B23" s="33">
         <v>4</v>
       </c>
-      <c r="C23" s="240" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" s="238"/>
-      <c r="E23" s="253"/>
-      <c r="F23" s="254"/>
+      <c r="C23" s="234" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="235"/>
+      <c r="E23" s="236"/>
+      <c r="F23" s="237"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="36"/>
       <c r="B24" s="37">
         <v>6</v>
       </c>
-      <c r="C24" s="180" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" s="181"/>
-      <c r="E24" s="181"/>
-      <c r="F24" s="182"/>
+      <c r="C24" s="182" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="183"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="184"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="30"/>
       <c r="B25" s="34">
         <v>7</v>
       </c>
-      <c r="C25" s="204" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="205"/>
-      <c r="E25" s="205"/>
-      <c r="F25" s="206"/>
+      <c r="C25" s="158" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="160"/>
     </row>
     <row r="26" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31" t="s">
@@ -4430,68 +4433,68 @@
       <c r="B26" s="32">
         <v>2</v>
       </c>
-      <c r="C26" s="259"/>
-      <c r="D26" s="260"/>
-      <c r="E26" s="261" t="s">
-        <v>134</v>
-      </c>
-      <c r="F26" s="262"/>
+      <c r="C26" s="242"/>
+      <c r="D26" s="243"/>
+      <c r="E26" s="244" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="245"/>
     </row>
     <row r="27" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="29"/>
       <c r="B27" s="33">
         <v>3</v>
       </c>
-      <c r="C27" s="179" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="160"/>
-      <c r="E27" s="160" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" s="161"/>
-    </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C27" s="178" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="163"/>
+    </row>
+    <row r="28" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="36"/>
       <c r="B28" s="37">
         <v>4</v>
       </c>
-      <c r="C28" s="232" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" s="233"/>
-      <c r="E28" s="234" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="235"/>
+      <c r="C28" s="262" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="263"/>
+      <c r="E28" s="264" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="265"/>
     </row>
     <row r="29" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="36"/>
       <c r="B29" s="37">
         <v>5</v>
       </c>
-      <c r="C29" s="172" t="s">
+      <c r="C29" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173" t="s">
-        <v>128</v>
-      </c>
-      <c r="F29" s="176"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="157"/>
     </row>
     <row r="30" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="36"/>
       <c r="B30" s="37">
         <v>6</v>
       </c>
-      <c r="C30" s="224" t="s">
+      <c r="C30" s="272" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225" t="s">
-        <v>129</v>
-      </c>
-      <c r="F30" s="226"/>
+      <c r="D30" s="273"/>
+      <c r="E30" s="273" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="274"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="28" t="s">
@@ -4500,64 +4503,64 @@
       <c r="B31" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="227" t="s">
+      <c r="C31" s="275" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="228"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="229"/>
+      <c r="D31" s="276"/>
+      <c r="E31" s="276"/>
+      <c r="F31" s="277"/>
     </row>
     <row r="32" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="38"/>
       <c r="B32" s="32">
         <v>4</v>
       </c>
-      <c r="C32" s="172" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173" t="s">
+      <c r="C32" s="155" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="176"/>
+      <c r="F32" s="157"/>
     </row>
     <row r="33" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="38"/>
       <c r="B33" s="32">
         <v>5</v>
       </c>
-      <c r="C33" s="240" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238" t="s">
-        <v>125</v>
-      </c>
-      <c r="F33" s="239"/>
+      <c r="C33" s="234" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" s="251"/>
     </row>
     <row r="34" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
       <c r="B34" s="33">
         <v>6</v>
       </c>
-      <c r="C34" s="210" t="s">
+      <c r="C34" s="166" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="211"/>
-      <c r="E34" s="238" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="239"/>
+      <c r="D34" s="167"/>
+      <c r="E34" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" s="251"/>
     </row>
     <row r="35" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="40"/>
       <c r="B35" s="34">
         <v>7</v>
       </c>
-      <c r="C35" s="250"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="209"/>
-      <c r="F35" s="252"/>
+      <c r="C35" s="230"/>
+      <c r="D35" s="231"/>
+      <c r="E35" s="165"/>
+      <c r="F35" s="232"/>
     </row>
     <row r="36" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="49" t="s">
@@ -4566,90 +4569,90 @@
       <c r="B36" s="35">
         <v>1</v>
       </c>
-      <c r="C36" s="246" t="s">
+      <c r="C36" s="258" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="247"/>
-      <c r="E36" s="248" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="249"/>
+      <c r="D36" s="259"/>
+      <c r="E36" s="260" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" s="261"/>
     </row>
     <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="41"/>
       <c r="B37" s="32">
         <v>2</v>
       </c>
-      <c r="C37" s="183" t="s">
+      <c r="C37" s="185" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="184"/>
-      <c r="E37" s="185" t="s">
+      <c r="D37" s="186"/>
+      <c r="E37" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="186"/>
+      <c r="F37" s="188"/>
     </row>
     <row r="38" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="42"/>
       <c r="B38" s="37">
         <v>3</v>
       </c>
-      <c r="C38" s="210" t="s">
+      <c r="C38" s="166" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="211"/>
-      <c r="E38" s="211" t="s">
+      <c r="D38" s="167"/>
+      <c r="E38" s="167" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="212"/>
+      <c r="F38" s="168"/>
     </row>
     <row r="39" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="42"/>
       <c r="B39" s="37">
         <v>4</v>
       </c>
-      <c r="C39" s="180" t="s">
+      <c r="C39" s="182" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="230"/>
-      <c r="E39" s="241" t="s">
+      <c r="D39" s="252"/>
+      <c r="E39" s="253" t="s">
         <v>61</v>
       </c>
-      <c r="F39" s="182"/>
+      <c r="F39" s="184"/>
     </row>
     <row r="40" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="42"/>
       <c r="B40" s="37">
         <v>5</v>
       </c>
-      <c r="C40" s="242"/>
-      <c r="D40" s="243"/>
-      <c r="E40" s="160" t="s">
+      <c r="C40" s="254"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="162" t="s">
         <v>45</v>
       </c>
-      <c r="F40" s="161"/>
+      <c r="F40" s="163"/>
     </row>
     <row r="41" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="43"/>
       <c r="B41" s="34">
         <v>6</v>
       </c>
-      <c r="C41" s="244"/>
-      <c r="D41" s="245"/>
-      <c r="E41" s="177" t="s">
+      <c r="C41" s="256"/>
+      <c r="D41" s="257"/>
+      <c r="E41" s="216" t="s">
         <v>45</v>
       </c>
-      <c r="F41" s="178"/>
+      <c r="F41" s="217"/>
     </row>
     <row r="42" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="236" t="s">
+      <c r="A42" s="249" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="236"/>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
+      <c r="B42" s="249"/>
+      <c r="C42" s="250"/>
+      <c r="D42" s="250"/>
+      <c r="E42" s="250"/>
+      <c r="F42" s="250"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="2" t="s">
@@ -4669,14 +4672,40 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:F27"/>
@@ -4693,40 +4722,14 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -4779,7 +4782,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>10</v>
@@ -4795,14 +4798,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -4810,7 +4813,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -4852,13 +4855,13 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
+        <v>78</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
@@ -4881,32 +4884,32 @@
       <c r="B10" s="32">
         <v>4</v>
       </c>
-      <c r="C10" s="303"/>
-      <c r="D10" s="304"/>
-      <c r="E10" s="304"/>
-      <c r="F10" s="305"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="279"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="280"/>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="29"/>
       <c r="B11" s="32">
         <v>5</v>
       </c>
-      <c r="C11" s="118" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120"/>
+      <c r="C11" s="120" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="122"/>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="29"/>
       <c r="B12" s="33">
         <v>6</v>
       </c>
-      <c r="C12" s="309"/>
-      <c r="D12" s="310"/>
-      <c r="E12" s="310"/>
-      <c r="F12" s="311"/>
+      <c r="C12" s="284"/>
+      <c r="D12" s="285"/>
+      <c r="E12" s="285"/>
+      <c r="F12" s="286"/>
     </row>
     <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="28" t="s">
@@ -4915,30 +4918,30 @@
       <c r="B13" s="35">
         <v>4</v>
       </c>
-      <c r="C13" s="306"/>
-      <c r="D13" s="307"/>
-      <c r="E13" s="307"/>
-      <c r="F13" s="308"/>
+      <c r="C13" s="281"/>
+      <c r="D13" s="282"/>
+      <c r="E13" s="282"/>
+      <c r="F13" s="283"/>
     </row>
     <row r="14" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="29"/>
       <c r="B14" s="33">
         <v>5</v>
       </c>
-      <c r="C14" s="297"/>
-      <c r="D14" s="298"/>
-      <c r="E14" s="298"/>
-      <c r="F14" s="299"/>
+      <c r="C14" s="287"/>
+      <c r="D14" s="288"/>
+      <c r="E14" s="288"/>
+      <c r="F14" s="289"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="36"/>
       <c r="B15" s="37">
         <v>6</v>
       </c>
-      <c r="C15" s="285"/>
-      <c r="D15" s="286"/>
-      <c r="E15" s="286"/>
-      <c r="F15" s="287"/>
+      <c r="C15" s="290"/>
+      <c r="D15" s="291"/>
+      <c r="E15" s="291"/>
+      <c r="F15" s="292"/>
     </row>
     <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="28" t="s">
@@ -4947,34 +4950,34 @@
       <c r="B16" s="35">
         <v>4</v>
       </c>
-      <c r="C16" s="300"/>
-      <c r="D16" s="301"/>
-      <c r="E16" s="301"/>
-      <c r="F16" s="302"/>
+      <c r="C16" s="293"/>
+      <c r="D16" s="294"/>
+      <c r="E16" s="294"/>
+      <c r="F16" s="295"/>
     </row>
     <row r="17" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="29"/>
       <c r="B17" s="33">
         <v>5</v>
       </c>
-      <c r="C17" s="294" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="295"/>
-      <c r="E17" s="295"/>
-      <c r="F17" s="296"/>
+      <c r="C17" s="296" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="297"/>
+      <c r="E17" s="297"/>
+      <c r="F17" s="298"/>
     </row>
     <row r="18" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="30"/>
       <c r="B18" s="34">
         <v>6</v>
       </c>
-      <c r="C18" s="148" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="150"/>
+      <c r="C18" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="68"/>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="28" t="s">
@@ -4983,32 +4986,32 @@
       <c r="B19" s="35">
         <v>4</v>
       </c>
-      <c r="C19" s="288"/>
-      <c r="D19" s="289"/>
-      <c r="E19" s="289"/>
-      <c r="F19" s="290"/>
+      <c r="C19" s="299"/>
+      <c r="D19" s="300"/>
+      <c r="E19" s="300"/>
+      <c r="F19" s="301"/>
     </row>
     <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="36"/>
       <c r="B20" s="33">
         <v>5</v>
       </c>
-      <c r="C20" s="294" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="295"/>
-      <c r="E20" s="295"/>
-      <c r="F20" s="296"/>
+      <c r="C20" s="296" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="297"/>
+      <c r="E20" s="297"/>
+      <c r="F20" s="298"/>
     </row>
     <row r="21" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="36"/>
       <c r="B21" s="34">
         <v>6</v>
       </c>
-      <c r="C21" s="285"/>
-      <c r="D21" s="286"/>
-      <c r="E21" s="286"/>
-      <c r="F21" s="287"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="291"/>
+      <c r="E21" s="291"/>
+      <c r="F21" s="292"/>
     </row>
     <row r="22" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="28" t="s">
@@ -5017,32 +5020,32 @@
       <c r="B22" s="35">
         <v>4</v>
       </c>
-      <c r="C22" s="291"/>
-      <c r="D22" s="292"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="293"/>
+      <c r="C22" s="302"/>
+      <c r="D22" s="303"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="304"/>
     </row>
     <row r="23" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="38"/>
       <c r="B23" s="33">
         <v>5</v>
       </c>
-      <c r="C23" s="297" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="298"/>
-      <c r="E23" s="298"/>
-      <c r="F23" s="299"/>
+      <c r="C23" s="287" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="288"/>
+      <c r="E23" s="288"/>
+      <c r="F23" s="289"/>
     </row>
     <row r="24" spans="1:6" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
       <c r="B24" s="37">
         <v>6</v>
       </c>
-      <c r="C24" s="285"/>
-      <c r="D24" s="286"/>
-      <c r="E24" s="286"/>
-      <c r="F24" s="287"/>
+      <c r="C24" s="290"/>
+      <c r="D24" s="291"/>
+      <c r="E24" s="291"/>
+      <c r="F24" s="292"/>
     </row>
     <row r="25" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="49" t="s">
@@ -5051,40 +5054,40 @@
       <c r="B25" s="35">
         <v>4</v>
       </c>
-      <c r="C25" s="278"/>
-      <c r="D25" s="279"/>
-      <c r="E25" s="279"/>
-      <c r="F25" s="280"/>
+      <c r="C25" s="305"/>
+      <c r="D25" s="306"/>
+      <c r="E25" s="306"/>
+      <c r="F25" s="307"/>
     </row>
     <row r="26" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="41"/>
       <c r="B26" s="32">
         <v>5</v>
       </c>
-      <c r="C26" s="281"/>
-      <c r="D26" s="282"/>
-      <c r="E26" s="282"/>
-      <c r="F26" s="283"/>
+      <c r="C26" s="308"/>
+      <c r="D26" s="309"/>
+      <c r="E26" s="309"/>
+      <c r="F26" s="310"/>
     </row>
     <row r="27" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="43"/>
       <c r="B27" s="34">
         <v>6</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="131"/>
     </row>
     <row r="28" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="284" t="s">
+      <c r="A28" s="311" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="284"/>
-      <c r="C28" s="284"/>
-      <c r="D28" s="284"/>
-      <c r="E28" s="284"/>
-      <c r="F28" s="284"/>
+      <c r="B28" s="311"/>
+      <c r="C28" s="311"/>
+      <c r="D28" s="311"/>
+      <c r="E28" s="311"/>
+      <c r="F28" s="311"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
@@ -5104,26 +5107,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -5176,7 +5179,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>10</v>
@@ -5192,14 +5195,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -5207,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -5241,7 +5244,7 @@
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>6</v>
@@ -5249,13 +5252,13 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
+        <v>78</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
@@ -5278,10 +5281,10 @@
       <c r="B10" s="32">
         <v>4</v>
       </c>
-      <c r="C10" s="303"/>
-      <c r="D10" s="304"/>
-      <c r="E10" s="304"/>
-      <c r="F10" s="305"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="279"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="280"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="29"/>
@@ -5298,10 +5301,10 @@
       <c r="B12" s="33">
         <v>6</v>
       </c>
-      <c r="C12" s="309"/>
-      <c r="D12" s="310"/>
-      <c r="E12" s="310"/>
-      <c r="F12" s="311"/>
+      <c r="C12" s="284"/>
+      <c r="D12" s="285"/>
+      <c r="E12" s="285"/>
+      <c r="F12" s="286"/>
     </row>
     <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="28" t="s">
@@ -5310,32 +5313,32 @@
       <c r="B13" s="35">
         <v>4</v>
       </c>
-      <c r="C13" s="306"/>
-      <c r="D13" s="307"/>
-      <c r="E13" s="307"/>
-      <c r="F13" s="308"/>
+      <c r="C13" s="281"/>
+      <c r="D13" s="282"/>
+      <c r="E13" s="282"/>
+      <c r="F13" s="283"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="29"/>
       <c r="B14" s="33">
         <v>5</v>
       </c>
-      <c r="C14" s="297" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="298"/>
-      <c r="E14" s="298"/>
-      <c r="F14" s="299"/>
+      <c r="C14" s="287" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="288"/>
+      <c r="E14" s="288"/>
+      <c r="F14" s="289"/>
     </row>
     <row r="15" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="36"/>
       <c r="B15" s="37">
         <v>6</v>
       </c>
-      <c r="C15" s="285"/>
-      <c r="D15" s="286"/>
-      <c r="E15" s="286"/>
-      <c r="F15" s="287"/>
+      <c r="C15" s="290"/>
+      <c r="D15" s="291"/>
+      <c r="E15" s="291"/>
+      <c r="F15" s="292"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="28" t="s">
@@ -5344,32 +5347,34 @@
       <c r="B16" s="35">
         <v>4</v>
       </c>
-      <c r="C16" s="300"/>
-      <c r="D16" s="301"/>
-      <c r="E16" s="301"/>
-      <c r="F16" s="302"/>
+      <c r="C16" s="293"/>
+      <c r="D16" s="294"/>
+      <c r="E16" s="294"/>
+      <c r="F16" s="295"/>
     </row>
     <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="29"/>
       <c r="B17" s="33">
         <v>5</v>
       </c>
-      <c r="C17" s="118" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
+      <c r="C17" s="120" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
     </row>
     <row r="18" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="30"/>
       <c r="B18" s="34">
         <v>6</v>
       </c>
-      <c r="C18" s="315"/>
-      <c r="D18" s="316"/>
-      <c r="E18" s="316"/>
-      <c r="F18" s="317"/>
+      <c r="C18" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="68"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="28" t="s">
@@ -5378,32 +5383,32 @@
       <c r="B19" s="35">
         <v>4</v>
       </c>
-      <c r="C19" s="288"/>
-      <c r="D19" s="289"/>
-      <c r="E19" s="289"/>
-      <c r="F19" s="290"/>
+      <c r="C19" s="299"/>
+      <c r="D19" s="300"/>
+      <c r="E19" s="300"/>
+      <c r="F19" s="301"/>
     </row>
     <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="36"/>
       <c r="B20" s="33">
         <v>5</v>
       </c>
-      <c r="C20" s="294" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="295"/>
-      <c r="E20" s="295"/>
-      <c r="F20" s="296"/>
+      <c r="C20" s="296" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="297"/>
+      <c r="E20" s="297"/>
+      <c r="F20" s="298"/>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="36"/>
       <c r="B21" s="34">
         <v>6</v>
       </c>
-      <c r="C21" s="285"/>
-      <c r="D21" s="286"/>
-      <c r="E21" s="286"/>
-      <c r="F21" s="287"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="291"/>
+      <c r="E21" s="291"/>
+      <c r="F21" s="292"/>
     </row>
     <row r="22" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="28" t="s">
@@ -5412,32 +5417,32 @@
       <c r="B22" s="35">
         <v>4</v>
       </c>
-      <c r="C22" s="291"/>
-      <c r="D22" s="292"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="293"/>
+      <c r="C22" s="302"/>
+      <c r="D22" s="303"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="304"/>
     </row>
     <row r="23" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="38"/>
       <c r="B23" s="33">
         <v>5</v>
       </c>
-      <c r="C23" s="294" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="295"/>
-      <c r="E23" s="295"/>
-      <c r="F23" s="296"/>
+      <c r="C23" s="296" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="297"/>
+      <c r="E23" s="297"/>
+      <c r="F23" s="298"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
       <c r="B24" s="37">
         <v>6</v>
       </c>
-      <c r="C24" s="285"/>
-      <c r="D24" s="286"/>
-      <c r="E24" s="286"/>
-      <c r="F24" s="287"/>
+      <c r="C24" s="290"/>
+      <c r="D24" s="291"/>
+      <c r="E24" s="291"/>
+      <c r="F24" s="292"/>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="49" t="s">
@@ -5446,42 +5451,42 @@
       <c r="B25" s="35">
         <v>4</v>
       </c>
-      <c r="C25" s="278"/>
-      <c r="D25" s="279"/>
-      <c r="E25" s="279"/>
-      <c r="F25" s="280"/>
+      <c r="C25" s="305"/>
+      <c r="D25" s="306"/>
+      <c r="E25" s="306"/>
+      <c r="F25" s="307"/>
     </row>
     <row r="26" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="41"/>
       <c r="B26" s="32">
         <v>5</v>
       </c>
-      <c r="C26" s="297" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="298"/>
-      <c r="E26" s="298"/>
-      <c r="F26" s="299"/>
+      <c r="C26" s="287" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="288"/>
+      <c r="E26" s="288"/>
+      <c r="F26" s="289"/>
     </row>
     <row r="27" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="43"/>
       <c r="B27" s="34">
         <v>6</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="131"/>
     </row>
     <row r="28" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="284" t="s">
+      <c r="A28" s="311" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="284"/>
-      <c r="C28" s="284"/>
-      <c r="D28" s="284"/>
-      <c r="E28" s="284"/>
-      <c r="F28" s="284"/>
+      <c r="B28" s="311"/>
+      <c r="C28" s="311"/>
+      <c r="D28" s="311"/>
+      <c r="E28" s="311"/>
+      <c r="F28" s="311"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
@@ -5501,6 +5506,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:F10"/>
@@ -5513,14 +5526,6 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -5573,7 +5578,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>10</v>
@@ -5589,14 +5594,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -5604,7 +5609,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -5638,7 +5643,7 @@
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>6</v>
@@ -5646,13 +5651,13 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
+        <v>78</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
@@ -5675,32 +5680,32 @@
       <c r="B10" s="32">
         <v>3</v>
       </c>
-      <c r="C10" s="303"/>
-      <c r="D10" s="304"/>
-      <c r="E10" s="304"/>
-      <c r="F10" s="305"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="279"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="280"/>
     </row>
     <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="29"/>
       <c r="B11" s="32">
         <v>4</v>
       </c>
-      <c r="C11" s="99" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="90"/>
+      <c r="C11" s="69" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="71"/>
     </row>
     <row r="12" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="29"/>
       <c r="B12" s="33">
         <v>5</v>
       </c>
-      <c r="C12" s="309"/>
-      <c r="D12" s="310"/>
-      <c r="E12" s="310"/>
-      <c r="F12" s="311"/>
+      <c r="C12" s="284"/>
+      <c r="D12" s="285"/>
+      <c r="E12" s="285"/>
+      <c r="F12" s="286"/>
     </row>
     <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="28" t="s">
@@ -5709,32 +5714,32 @@
       <c r="B13" s="35">
         <v>3</v>
       </c>
-      <c r="C13" s="306"/>
-      <c r="D13" s="307"/>
-      <c r="E13" s="307"/>
-      <c r="F13" s="308"/>
+      <c r="C13" s="281"/>
+      <c r="D13" s="282"/>
+      <c r="E13" s="282"/>
+      <c r="F13" s="283"/>
     </row>
     <row r="14" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="29"/>
       <c r="B14" s="33">
         <v>4</v>
       </c>
-      <c r="C14" s="297" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="298"/>
-      <c r="E14" s="298"/>
-      <c r="F14" s="299"/>
+      <c r="C14" s="287" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="288"/>
+      <c r="E14" s="288"/>
+      <c r="F14" s="289"/>
     </row>
     <row r="15" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="36"/>
       <c r="B15" s="37">
         <v>5</v>
       </c>
-      <c r="C15" s="285"/>
-      <c r="D15" s="286"/>
-      <c r="E15" s="286"/>
-      <c r="F15" s="287"/>
+      <c r="C15" s="290"/>
+      <c r="D15" s="291"/>
+      <c r="E15" s="291"/>
+      <c r="F15" s="292"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="28" t="s">
@@ -5743,32 +5748,32 @@
       <c r="B16" s="35">
         <v>3</v>
       </c>
-      <c r="C16" s="300"/>
-      <c r="D16" s="301"/>
-      <c r="E16" s="301"/>
-      <c r="F16" s="302"/>
+      <c r="C16" s="293"/>
+      <c r="D16" s="294"/>
+      <c r="E16" s="294"/>
+      <c r="F16" s="295"/>
     </row>
     <row r="17" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="29"/>
       <c r="B17" s="33">
         <v>4</v>
       </c>
-      <c r="C17" s="118" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
+      <c r="C17" s="120" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
     </row>
     <row r="18" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="30"/>
       <c r="B18" s="37">
         <v>5</v>
       </c>
-      <c r="C18" s="315"/>
-      <c r="D18" s="316"/>
-      <c r="E18" s="316"/>
-      <c r="F18" s="317"/>
+      <c r="C18" s="318"/>
+      <c r="D18" s="319"/>
+      <c r="E18" s="319"/>
+      <c r="F18" s="320"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="28" t="s">
@@ -5777,30 +5782,30 @@
       <c r="B19" s="35">
         <v>3</v>
       </c>
-      <c r="C19" s="288"/>
-      <c r="D19" s="289"/>
-      <c r="E19" s="289"/>
-      <c r="F19" s="290"/>
+      <c r="C19" s="299"/>
+      <c r="D19" s="300"/>
+      <c r="E19" s="300"/>
+      <c r="F19" s="301"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="36"/>
       <c r="B20" s="33">
         <v>4</v>
       </c>
-      <c r="C20" s="318"/>
-      <c r="D20" s="319"/>
-      <c r="E20" s="319"/>
-      <c r="F20" s="320"/>
+      <c r="C20" s="315"/>
+      <c r="D20" s="316"/>
+      <c r="E20" s="316"/>
+      <c r="F20" s="317"/>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="36"/>
       <c r="B21" s="37">
         <v>5</v>
       </c>
-      <c r="C21" s="285"/>
-      <c r="D21" s="286"/>
-      <c r="E21" s="286"/>
-      <c r="F21" s="287"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="291"/>
+      <c r="E21" s="291"/>
+      <c r="F21" s="292"/>
     </row>
     <row r="22" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="28" t="s">
@@ -5809,30 +5814,30 @@
       <c r="B22" s="35">
         <v>3</v>
       </c>
-      <c r="C22" s="291"/>
-      <c r="D22" s="292"/>
-      <c r="E22" s="292"/>
-      <c r="F22" s="293"/>
+      <c r="C22" s="302"/>
+      <c r="D22" s="303"/>
+      <c r="E22" s="303"/>
+      <c r="F22" s="304"/>
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="38"/>
       <c r="B23" s="33">
         <v>4</v>
       </c>
-      <c r="C23" s="318"/>
-      <c r="D23" s="319"/>
-      <c r="E23" s="319"/>
-      <c r="F23" s="320"/>
+      <c r="C23" s="315"/>
+      <c r="D23" s="316"/>
+      <c r="E23" s="316"/>
+      <c r="F23" s="317"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
       <c r="B24" s="37">
         <v>5</v>
       </c>
-      <c r="C24" s="285"/>
-      <c r="D24" s="286"/>
-      <c r="E24" s="286"/>
-      <c r="F24" s="287"/>
+      <c r="C24" s="290"/>
+      <c r="D24" s="291"/>
+      <c r="E24" s="291"/>
+      <c r="F24" s="292"/>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="49" t="s">
@@ -5841,42 +5846,42 @@
       <c r="B25" s="35">
         <v>3</v>
       </c>
-      <c r="C25" s="278"/>
-      <c r="D25" s="279"/>
-      <c r="E25" s="279"/>
-      <c r="F25" s="280"/>
+      <c r="C25" s="305"/>
+      <c r="D25" s="306"/>
+      <c r="E25" s="306"/>
+      <c r="F25" s="307"/>
     </row>
     <row r="26" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="41"/>
       <c r="B26" s="32">
         <v>4</v>
       </c>
-      <c r="C26" s="297" t="s">
-        <v>148</v>
-      </c>
-      <c r="D26" s="298"/>
-      <c r="E26" s="298"/>
-      <c r="F26" s="299"/>
+      <c r="C26" s="287" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="288"/>
+      <c r="E26" s="288"/>
+      <c r="F26" s="289"/>
     </row>
     <row r="27" spans="1:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="43"/>
       <c r="B27" s="34">
         <v>5</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="131"/>
     </row>
     <row r="28" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="284" t="s">
+      <c r="A28" s="311" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="284"/>
-      <c r="C28" s="284"/>
-      <c r="D28" s="284"/>
-      <c r="E28" s="284"/>
-      <c r="F28" s="284"/>
+      <c r="B28" s="311"/>
+      <c r="C28" s="311"/>
+      <c r="D28" s="311"/>
+      <c r="E28" s="311"/>
+      <c r="F28" s="311"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
@@ -5896,14 +5901,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C10:F10"/>
@@ -5916,6 +5913,14 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5">
